--- a/r5-ELGA-MOPED-Aenderungen-von-Main-in-Hackathon-nachziehen/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Aenderungen-von-Main-in-Hackathon-nachziehen/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:25:53+00:00</t>
+    <t>2025-02-12T16:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
